--- a/Compititor's_Price/Recticel_Prices/Recticel_Prices_07-07-2025.xlsx
+++ b/Compititor's_Price/Recticel_Prices/Recticel_Prices_07-07-2025.xlsx
@@ -568,7 +568,7 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>£12.12</t>
+          <t>£11.00</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
@@ -665,7 +665,7 @@
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>£13.33</t>
+          <t>£13.15</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
@@ -762,7 +762,7 @@
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>£18.00</t>
+          <t>£15.55</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
@@ -859,7 +859,7 @@
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>£17.48</t>
+          <t>£17.88</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
@@ -956,7 +956,7 @@
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>£24.48</t>
+          <t>£21.00</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
@@ -1053,7 +1053,7 @@
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>£24.68</t>
+          <t>£24.75</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
@@ -1150,7 +1150,7 @@
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>£25.00</t>
+          <t>POA or OOS</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
@@ -1247,7 +1247,7 @@
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>£28.88</t>
+          <t>£28.00</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
@@ -1344,7 +1344,7 @@
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>£30.00</t>
+          <t>£28.58</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>£31.62</t>
+          <t>£28.50</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
@@ -1538,7 +1538,7 @@
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>£41.18</t>
+          <t>£37.14</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
@@ -1635,7 +1635,7 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>£38.82</t>
+          <t>£36.88</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
@@ -1732,7 +1732,7 @@
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>£46.00</t>
+          <t>£41.48</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
@@ -1829,7 +1829,7 @@
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>£46.88</t>
+          <t>£43.00</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
@@ -1926,7 +1926,7 @@
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>£48.00</t>
+          <t>£42.48</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="Q16" t="inlineStr">
         <is>
-          <t>Error: ('Connection aborted.', ConnectionResetError(10054, 'An existing connection was forcibly closed by the remote host', None, 10054, None))</t>
+          <t>Price Not Found</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
